--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N23_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N23_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>40.44882407594177</v>
+        <v>6.572933912340538</v>
       </c>
       <c r="D2" t="n">
-        <v>40.79070649006765</v>
+        <v>6.628489804635993</v>
       </c>
       <c r="E2" t="n">
-        <v>16.21316876172537</v>
+        <v>2.634639923780373</v>
       </c>
       <c r="F2" t="n">
-        <v>8.934744554724977</v>
+        <v>1.451895990142809</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>19.37874662902711</v>
+        <v>3.149046327216906</v>
       </c>
       <c r="D3" t="n">
-        <v>19.72269732610234</v>
+        <v>3.20493831549163</v>
       </c>
       <c r="E3" t="n">
-        <v>16.21316876172537</v>
+        <v>2.634639923780373</v>
       </c>
       <c r="F3" t="n">
-        <v>8.934744554724977</v>
+        <v>1.451895990142809</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>49.72209362581211</v>
+        <v>8.079840214194469</v>
       </c>
       <c r="D4" t="n">
-        <v>34.57540094111356</v>
+        <v>5.618502652930954</v>
       </c>
       <c r="E4" t="n">
-        <v>16.21316876172537</v>
+        <v>2.634639923780373</v>
       </c>
       <c r="F4" t="n">
-        <v>8.934744554724977</v>
+        <v>1.451895990142809</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>28.46939800867865</v>
+        <v>4.626277176410281</v>
       </c>
       <c r="D5" t="n">
-        <v>28.84510626555971</v>
+        <v>4.687329768153454</v>
       </c>
       <c r="E5" t="n">
-        <v>16.21316876172537</v>
+        <v>2.634639923780373</v>
       </c>
       <c r="F5" t="n">
-        <v>8.934744554724977</v>
+        <v>1.451895990142809</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>60.7564280488887</v>
+        <v>9.872919557944414</v>
       </c>
       <c r="D6" t="n">
-        <v>28.33024716631271</v>
+        <v>4.603665164525815</v>
       </c>
       <c r="E6" t="n">
-        <v>16.21316876172537</v>
+        <v>2.634639923780373</v>
       </c>
       <c r="F6" t="n">
-        <v>8.934744554724977</v>
+        <v>1.451895990142809</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>13.57880706943329</v>
+        <v>2.20655614878291</v>
       </c>
       <c r="D7" t="n">
-        <v>13.65770443229757</v>
+        <v>2.219376970248355</v>
       </c>
       <c r="E7" t="n">
-        <v>16.21316876172537</v>
+        <v>2.634639923780373</v>
       </c>
       <c r="F7" t="n">
-        <v>8.934744554724977</v>
+        <v>1.451895990142809</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>19.34491989715949</v>
+        <v>3.143549483288417</v>
       </c>
       <c r="D8" t="n">
-        <v>19.69975912054814</v>
+        <v>3.201210857089074</v>
       </c>
       <c r="E8" t="n">
-        <v>16.21316876172537</v>
+        <v>2.634639923780373</v>
       </c>
       <c r="F8" t="n">
-        <v>8.934744554724977</v>
+        <v>1.451895990142809</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>60.42290871868888</v>
+        <v>9.818722666786943</v>
       </c>
       <c r="D9" t="n">
-        <v>15.00276692369284</v>
+        <v>2.437949625100087</v>
       </c>
       <c r="E9" t="n">
-        <v>16.21316876172537</v>
+        <v>2.634639923780373</v>
       </c>
       <c r="F9" t="n">
-        <v>8.934744554724977</v>
+        <v>1.451895990142809</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>41.26528530925166</v>
+        <v>6.705608862753395</v>
       </c>
       <c r="D10" t="n">
-        <v>28.79286786006989</v>
+        <v>4.678841027261357</v>
       </c>
       <c r="E10" t="n">
-        <v>16.21316876172537</v>
+        <v>2.634639923780373</v>
       </c>
       <c r="F10" t="n">
-        <v>8.934744554724977</v>
+        <v>1.451895990142809</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>54.98959412825818</v>
+        <v>8.935809045841955</v>
       </c>
       <c r="D11" t="n">
-        <v>11.77214735948602</v>
+        <v>1.912973945916478</v>
       </c>
       <c r="E11" t="n">
-        <v>16.21316876172537</v>
+        <v>2.634639923780373</v>
       </c>
       <c r="F11" t="n">
-        <v>8.934744554724977</v>
+        <v>1.451895990142809</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>47.2625563718133</v>
+        <v>7.680165410419662</v>
       </c>
       <c r="D12" t="n">
-        <v>30.13349926208003</v>
+        <v>4.896693630088006</v>
       </c>
       <c r="E12" t="n">
-        <v>16.21316876172537</v>
+        <v>2.634639923780373</v>
       </c>
       <c r="F12" t="n">
-        <v>8.934744554724977</v>
+        <v>1.451895990142809</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>40.08853717460279</v>
+        <v>6.514387290872953</v>
       </c>
       <c r="D13" t="n">
-        <v>39.93331465576731</v>
+        <v>6.489163631562189</v>
       </c>
       <c r="E13" t="n">
-        <v>16.21316876172537</v>
+        <v>2.634639923780373</v>
       </c>
       <c r="F13" t="n">
-        <v>8.934744554724977</v>
+        <v>1.451895990142809</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>31.08283439777286</v>
+        <v>5.050960589638089</v>
       </c>
       <c r="D14" t="n">
-        <v>31.23602844652023</v>
+        <v>5.075854622559538</v>
       </c>
       <c r="E14" t="n">
-        <v>16.21316876172537</v>
+        <v>2.634639923780373</v>
       </c>
       <c r="F14" t="n">
-        <v>8.934744554724977</v>
+        <v>1.451895990142809</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>21.29813308074094</v>
+        <v>3.460946625620402</v>
       </c>
       <c r="D15" t="n">
-        <v>20.79085218716437</v>
+        <v>3.37851348041421</v>
       </c>
       <c r="E15" t="n">
-        <v>16.21316876172537</v>
+        <v>2.634639923780373</v>
       </c>
       <c r="F15" t="n">
-        <v>8.934744554724977</v>
+        <v>1.451895990142809</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>16.7321184424648</v>
+        <v>2.718969246900529</v>
       </c>
       <c r="D16" t="n">
-        <v>16.63194080477903</v>
+        <v>2.702690380776593</v>
       </c>
       <c r="E16" t="n">
-        <v>16.21316876172537</v>
+        <v>2.634639923780373</v>
       </c>
       <c r="F16" t="n">
-        <v>8.934744554724977</v>
+        <v>1.451895990142809</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>12.04941929953722</v>
+        <v>1.958030636174798</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8910639086021</v>
+        <v>1.932297885147841</v>
       </c>
       <c r="E17" t="n">
-        <v>16.21316876172537</v>
+        <v>2.634639923780373</v>
       </c>
       <c r="F17" t="n">
-        <v>8.934744554724977</v>
+        <v>1.451895990142809</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>22.66984138462168</v>
+        <v>3.683849225001023</v>
       </c>
       <c r="D18" t="n">
-        <v>22.60204122558316</v>
+        <v>3.672831699157264</v>
       </c>
       <c r="E18" t="n">
-        <v>16.21316876172537</v>
+        <v>2.634639923780373</v>
       </c>
       <c r="F18" t="n">
-        <v>8.934744554724977</v>
+        <v>1.451895990142809</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>14.03411840466328</v>
+        <v>2.280544240757783</v>
       </c>
       <c r="D19" t="n">
-        <v>13.93985889870758</v>
+        <v>2.265227071039983</v>
       </c>
       <c r="E19" t="n">
-        <v>16.21316876172537</v>
+        <v>2.634639923780373</v>
       </c>
       <c r="F19" t="n">
-        <v>8.934744554724977</v>
+        <v>1.451895990142809</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>16.6971281525944</v>
+        <v>2.71328332479659</v>
       </c>
       <c r="D20" t="n">
-        <v>18.54886378398007</v>
+        <v>3.014190364896761</v>
       </c>
       <c r="E20" t="n">
-        <v>16.21316876172537</v>
+        <v>2.634639923780373</v>
       </c>
       <c r="F20" t="n">
-        <v>8.934744554724977</v>
+        <v>1.451895990142809</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
